--- a/AAII_Financials/Quarterly/FOSUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOSUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="92">
   <si>
     <t>FOSUY</t>
   </si>
@@ -656,68 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -757,8 +769,20 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -798,8 +822,20 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -839,8 +875,20 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -856,8 +904,12 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -897,8 +949,20 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -938,8 +1002,20 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -979,8 +1055,20 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1020,8 +1108,20 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1034,8 +1134,12 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1075,8 +1179,20 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1116,8 +1232,20 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1133,8 +1261,12 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1174,8 +1306,20 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1215,8 +1359,20 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1256,8 +1412,20 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1297,8 +1465,20 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1338,8 +1518,20 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1379,8 +1571,20 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1420,8 +1624,20 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1461,8 +1677,20 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1502,8 +1730,20 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1543,8 +1783,20 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1584,8 +1836,20 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1625,8 +1889,20 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1666,8 +1942,20 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1707,8 +1995,20 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1748,8 +2048,20 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1789,54 +2101,78 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1852,8 +2188,12 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1869,377 +2209,489 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9011500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8874900</v>
+      </c>
+      <c r="F41" s="3">
+        <v>8734500</v>
+      </c>
+      <c r="G41" s="3">
+        <v>8581400</v>
+      </c>
+      <c r="H41" s="3">
         <v>9468400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="I41" s="3">
         <v>9347500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>14568800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>15159900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>15075700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>15172600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>13039200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>12671600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>15812900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>16694800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="R41" s="3">
         <v>14580400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="S41" s="3">
         <v>14135500</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6301700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>6206100</v>
+      </c>
+      <c r="F42" s="3">
+        <v>6469100</v>
+      </c>
+      <c r="G42" s="3">
+        <v>6355700</v>
+      </c>
+      <c r="H42" s="3">
         <v>6101900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="I42" s="3">
         <v>6024000</v>
       </c>
-      <c r="F42" s="3">
-        <v>7048700</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="J42" s="3">
+        <v>7010000</v>
+      </c>
+      <c r="K42" s="3">
         <v>7334700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="L42" s="3">
         <v>7231300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="M42" s="3">
         <v>7277800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="N42" s="3">
         <v>8488400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="O42" s="3">
         <v>8249100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="P42" s="3">
         <v>7892000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="Q42" s="3">
         <v>8332100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="R42" s="3">
         <v>9674900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="S42" s="3">
         <v>9379600</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5121000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5043300</v>
+      </c>
+      <c r="F43" s="3">
+        <v>7471400</v>
+      </c>
+      <c r="G43" s="3">
+        <v>7340400</v>
+      </c>
+      <c r="H43" s="3">
         <v>5775700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="I43" s="3">
         <v>5702000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>10972000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="K43" s="3">
         <v>11417200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>9151800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>9210600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>11457600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>11134600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>7970200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>8414700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="R43" s="3">
         <v>10278100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="S43" s="3">
         <v>9964400</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8092600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>7969900</v>
+      </c>
+      <c r="F44" s="3">
+        <v>8720200</v>
+      </c>
+      <c r="G44" s="3">
+        <v>8567300</v>
+      </c>
+      <c r="H44" s="3">
         <v>9384600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="I44" s="3">
         <v>9264700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="J44" s="3">
         <v>9715400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="K44" s="3">
         <v>10109600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>12006300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>12083400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>12744200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>12385000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>13999900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>14780700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="R44" s="3">
         <v>15121600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="S44" s="3">
         <v>14660200</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>422100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>415700</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1494200</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1468000</v>
+      </c>
+      <c r="H45" s="3">
         <v>219800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="I45" s="3">
         <v>217000</v>
       </c>
-      <c r="F45" s="3">
-        <v>1200200</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="J45" s="3">
+        <v>1239000</v>
+      </c>
+      <c r="K45" s="3">
         <v>1248900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>594700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>598600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>1475600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>1434000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>2257600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>2383500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="R45" s="3">
         <v>4174700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="S45" s="3">
         <v>4047300</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33562100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>33053100</v>
+      </c>
+      <c r="F46" s="3">
+        <v>33881600</v>
+      </c>
+      <c r="G46" s="3">
+        <v>33287600</v>
+      </c>
+      <c r="H46" s="3">
         <v>35941000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="I46" s="3">
         <v>35481800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>44330600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>46129300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>48823600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>49137300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>48115100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>46758700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>52776200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>55719500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="R46" s="3">
         <v>54579600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="S46" s="3">
         <v>52914100</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>27571400</v>
+      </c>
+      <c r="E47" s="3">
+        <v>27153300</v>
+      </c>
+      <c r="F47" s="3">
+        <v>26800400</v>
+      </c>
+      <c r="G47" s="3">
+        <v>26330600</v>
+      </c>
+      <c r="H47" s="3">
         <v>26300000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="I47" s="3">
         <v>25964000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="J47" s="3">
         <v>26808800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="K47" s="3">
         <v>27896500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="L47" s="3">
         <v>25795000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="M47" s="3">
         <v>25960800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>26147500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>25410300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>25121900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>26523000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="R47" s="3">
         <v>24651700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="S47" s="3">
         <v>23899400</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11948300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>11767100</v>
+      </c>
+      <c r="F48" s="3">
+        <v>11969200</v>
+      </c>
+      <c r="G48" s="3">
+        <v>11759400</v>
+      </c>
+      <c r="H48" s="3">
         <v>11778900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
         <v>11628400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="J48" s="3">
         <v>11156500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>11609200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>10935500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>11005700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>11692100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>11362500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>10174200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>10741600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="R48" s="3">
         <v>10137700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="S48" s="3">
         <v>9828300</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9119000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>8980700</v>
+      </c>
+      <c r="F49" s="3">
+        <v>8016800</v>
+      </c>
+      <c r="G49" s="3">
+        <v>7876300</v>
+      </c>
+      <c r="H49" s="3">
         <v>9130700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="I49" s="3">
         <v>9014000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="J49" s="3">
         <v>7992800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="K49" s="3">
         <v>8317100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>9065600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
         <v>9123800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="N49" s="3">
         <v>8807000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>8558700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="P49" s="3">
         <v>8896600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="Q49" s="3">
         <v>9392700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="R49" s="3">
         <v>8444700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="S49" s="3">
         <v>8187000</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2279,8 +2731,20 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2320,49 +2784,73 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21458500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>21133000</v>
+      </c>
+      <c r="F52" s="3">
+        <v>19711700</v>
+      </c>
+      <c r="G52" s="3">
+        <v>19366200</v>
+      </c>
+      <c r="H52" s="3">
         <v>18368400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="I52" s="3">
         <v>18133800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="J52" s="3">
         <v>17079800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="K52" s="3">
         <v>17772800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>17127200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>17237300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>17315700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>16827500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>16989000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>17936400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="R52" s="3">
         <v>17256300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="S52" s="3">
         <v>16729700</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2402,49 +2890,73 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>104859900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>103269700</v>
+      </c>
+      <c r="F54" s="3">
+        <v>102400300</v>
+      </c>
+      <c r="G54" s="3">
+        <v>100605200</v>
+      </c>
+      <c r="H54" s="3">
         <v>102695100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="I54" s="3">
         <v>101383200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>109126900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>113554500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>113100200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>113827000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>114003500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>110789600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>115118600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>121538900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="R54" s="3">
         <v>116913600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="S54" s="3">
         <v>113345800</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2460,8 +2972,12 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2477,254 +2993,330 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2872800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2829200</v>
+      </c>
+      <c r="F57" s="3">
+        <v>3834000</v>
+      </c>
+      <c r="G57" s="3">
+        <v>3766700</v>
+      </c>
+      <c r="H57" s="3">
         <v>3024700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
         <v>2986000</v>
       </c>
-      <c r="F57" s="3">
-        <v>3173900</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="J57" s="3">
+        <v>4019500</v>
+      </c>
+      <c r="K57" s="3">
         <v>3302700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>3464300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>3486600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>3739500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>3634100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>3389000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>3578000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="R57" s="3">
         <v>3677600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="S57" s="3">
         <v>3565400</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>15478600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>15243900</v>
+      </c>
+      <c r="F58" s="3">
+        <v>15538400</v>
+      </c>
+      <c r="G58" s="3">
+        <v>15266000</v>
+      </c>
+      <c r="H58" s="3">
         <v>15965300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="I58" s="3">
         <v>15761300</v>
       </c>
-      <c r="F58" s="3">
-        <v>15888700</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="J58" s="3">
+        <v>16226300</v>
+      </c>
+      <c r="K58" s="3">
         <v>16533300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="L58" s="3">
         <v>16704900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="M58" s="3">
         <v>16812300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="N58" s="3">
         <v>14007100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>13612200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>2077000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="Q58" s="3">
         <v>2192900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="R58" s="3">
         <v>15995200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="S58" s="3">
         <v>15507100</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8449700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>8321500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>8865700</v>
+      </c>
+      <c r="G59" s="3">
+        <v>8710300</v>
+      </c>
+      <c r="H59" s="3">
         <v>8409900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="I59" s="3">
         <v>8302400</v>
       </c>
-      <c r="F59" s="3">
-        <v>9080500</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="J59" s="3">
+        <v>7897400</v>
+      </c>
+      <c r="K59" s="3">
         <v>9448900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>14523100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>14616400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>9895500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>9616500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>6216500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>6563200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="R59" s="3">
         <v>11533800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="S59" s="3">
         <v>11181800</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35619400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>35079200</v>
+      </c>
+      <c r="F60" s="3">
+        <v>30326000</v>
+      </c>
+      <c r="G60" s="3">
+        <v>29794400</v>
+      </c>
+      <c r="H60" s="3">
         <v>35209800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
         <v>34760000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>30102400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>31323700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>40938200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>41201300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>29623000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>28787900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>22665600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>23929600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="R60" s="3">
         <v>33200100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="S60" s="3">
         <v>32186900</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16659600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>16406900</v>
+      </c>
+      <c r="F61" s="3">
+        <v>20310800</v>
+      </c>
+      <c r="G61" s="3">
+        <v>19954800</v>
+      </c>
+      <c r="H61" s="3">
         <v>15038800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="I61" s="3">
         <v>14846700</v>
       </c>
-      <c r="F61" s="3">
-        <v>16708300</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="J61" s="3">
+        <v>17095500</v>
+      </c>
+      <c r="K61" s="3">
         <v>17386200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>14557300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>14650900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>19004800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>18469100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>30247200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="Q61" s="3">
         <v>31934100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="R61" s="3">
         <v>19787200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="S61" s="3">
         <v>19183400</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23944700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>23581600</v>
+      </c>
+      <c r="F62" s="3">
+        <v>24748200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>24314400</v>
+      </c>
+      <c r="H62" s="3">
         <v>21710700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="I62" s="3">
         <v>21433400</v>
       </c>
-      <c r="F62" s="3">
-        <v>32224100</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="J62" s="3">
+        <v>31836900</v>
+      </c>
+      <c r="K62" s="3">
         <v>33531600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>23009900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>23157800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>32490400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>31574500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>30565300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>32269900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="R62" s="3">
         <v>31360500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="S62" s="3">
         <v>30403500</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2764,8 +3356,20 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2805,8 +3409,20 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2846,49 +3462,73 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>79338700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>78135500</v>
+      </c>
+      <c r="F66" s="3">
+        <v>78338800</v>
+      </c>
+      <c r="G66" s="3">
+        <v>76965500</v>
+      </c>
+      <c r="H66" s="3">
         <v>75149100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="I66" s="3">
         <v>74189100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>82063400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>85393000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>84308700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>84850500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>84589100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>82204400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>86801300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>91642300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>88050400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="S66" s="3">
         <v>85363500</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2904,8 +3544,12 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2945,8 +3589,20 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2986,8 +3642,20 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3027,8 +3695,20 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3068,49 +3748,73 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8943300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>8807700</v>
+      </c>
+      <c r="F72" s="3">
+        <v>8468700</v>
+      </c>
+      <c r="G72" s="3">
+        <v>8320300</v>
+      </c>
+      <c r="H72" s="3">
         <v>11626400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="I72" s="3">
         <v>11477800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
         <v>11356800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="K72" s="3">
         <v>11817600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>12110400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>12188200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>12367100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>12018500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>12512900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>13210800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="R72" s="3">
         <v>12557600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="S72" s="3">
         <v>12174400</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3150,8 +3854,20 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3191,8 +3907,20 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3232,49 +3960,73 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14013100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>13800600</v>
+      </c>
+      <c r="F76" s="3">
+        <v>13414900</v>
+      </c>
+      <c r="G76" s="3">
+        <v>13179700</v>
+      </c>
+      <c r="H76" s="3">
         <v>16491000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="I76" s="3">
         <v>16280300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>16180500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>16837000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>17180600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>17291000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>17619300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>17122600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>17269200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>18232400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>17504700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="S76" s="3">
         <v>16970600</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3314,54 +4066,78 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3401,8 +4177,20 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3418,49 +4206,65 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>283400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>279800</v>
+      </c>
+      <c r="F83" s="3">
+        <v>294700</v>
+      </c>
+      <c r="G83" s="3">
+        <v>306600</v>
+      </c>
+      <c r="H83" s="3">
         <v>278900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="I83" s="3">
         <v>280700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="J83" s="3">
         <v>292300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="K83" s="3">
         <v>284000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="L83" s="3">
         <v>252700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="M83" s="3">
         <v>266800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="N83" s="3">
         <v>260900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="O83" s="3">
         <v>253000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="P83" s="3">
         <v>236000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="Q83" s="3">
         <v>249300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="R83" s="3">
         <v>239300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="S83" s="3">
         <v>235900</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3500,8 +4304,20 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3541,8 +4357,20 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3582,8 +4410,20 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3623,8 +4463,20 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3664,49 +4516,73 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1350000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1329500</v>
+      </c>
+      <c r="F89" s="3">
+        <v>856500</v>
+      </c>
+      <c r="G89" s="3">
+        <v>841500</v>
+      </c>
+      <c r="H89" s="3">
         <v>1019400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="I89" s="3">
         <v>1006400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="J89" s="3">
         <v>1112200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
         <v>1157300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>732700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>737400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>-376400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>-365800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>1045300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>1103600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="R89" s="3">
         <v>-450600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="S89" s="3">
         <v>-436800</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3722,49 +4598,65 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-360500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-355100</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-271500</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-266700</v>
+      </c>
+      <c r="H91" s="3">
         <v>-290900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="I91" s="3">
         <v>-287100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="J91" s="3">
         <v>-207900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="K91" s="3">
         <v>-216300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-308700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="M91" s="3">
         <v>-310700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
         <v>-342800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-333100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="P91" s="3">
         <v>-322000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="Q91" s="3">
         <v>-339900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="R91" s="3">
         <v>-211800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="S91" s="3">
         <v>-205300</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3804,8 +4696,20 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3845,49 +4749,73 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-520500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-512600</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-679900</v>
+      </c>
+      <c r="H94" s="3">
         <v>-3590800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="I94" s="3">
         <v>-3545000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="J94" s="3">
         <v>-186400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="K94" s="3">
         <v>-194000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>178500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>179700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
         <v>-54900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>-53300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>1266200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="Q94" s="3">
         <v>1336800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="R94" s="3">
         <v>2099300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="S94" s="3">
         <v>2035200</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3903,49 +4831,65 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G96" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H96" s="3">
         <v>12200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="I96" s="3">
         <v>12000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="J96" s="3">
         <v>16500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="K96" s="3">
         <v>17100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="L96" s="3">
         <v>800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="M96" s="3">
         <v>800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="N96" s="3">
         <v>2500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="O96" s="3">
         <v>2500</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3">
         <v>136000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="S96" s="3">
         <v>131800</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3985,8 +4929,20 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4026,8 +4982,20 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4067,57 +5035,81 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-500100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-492500</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-507600</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-498700</v>
+      </c>
+      <c r="H100" s="3">
         <v>-569000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="I100" s="3">
         <v>-561800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="J100" s="3">
         <v>-1237200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="K100" s="3">
         <v>-1287400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>260900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>262600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
         <v>-1303700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>-1267000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>-1460000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="Q100" s="3">
         <v>-1541500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="R100" s="3">
         <v>-3296100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="S100" s="3">
         <v>-3195500</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>4</v>
+      <c r="D101" s="3">
+        <v>485100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>478900</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>4</v>
@@ -4149,45 +5141,69 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>242800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>239100</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-391100</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-384300</v>
+      </c>
+      <c r="H102" s="3">
         <v>-2655400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="I102" s="3">
         <v>-2621400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="J102" s="3">
         <v>-311500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="K102" s="3">
         <v>-324100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>1172100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>1179700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>-1735000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>-1686100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>851500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>899000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="R102" s="3">
         <v>-1647400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="S102" s="3">
         <v>-1597100</v>
       </c>
     </row>
